--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -814,6 +814,97 @@
       </c>
       <c r="C27" s="4" t="n">
         <v>9.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Πέννες με κιμά</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Πέννες a la creme</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Κοτόπουλο με μπάμιες</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Χοιρινό λεμονάτο</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Σπετσοφάι</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Χταπόδι με κοφτό μακαρόνι</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Γιουβέτσι με χταπόδι</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1045,6 +1136,32 @@
       </c>
       <c r="C16" s="4" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Σνίτσελ χοιρινό</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Φιλέτο κοτόπουλο a la creme</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -1373,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1520,6 +1637,19 @@
       </c>
       <c r="C11" s="4" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Pancake σοκολάτα &amp; μπισκότο</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -1533,7 +1663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1738,6 +1868,58 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Fanta πορτοκαλάδα μπλε 330ml</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Fanta λεμονάδα 330ml</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Coca-Cola 500ml</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Amita πορτοκάλι, βερύκοκο &amp; μήλο 250ml</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Μαγειρευτά" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Της ώρας" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Συνοδευτικά" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Σαλάτες" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Γλυκά" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Αναψυκτικά - Ποτά" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Μαγειρευτά" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Της ώρας" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Συνοδευτικά" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Σαλάτες" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Γλυκά" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Αναψυκτικά - Ποτά" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -88,6 +88,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -814,6 +815,84 @@
       </c>
       <c r="C27" s="4" t="n">
         <v>9.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ψαρόσουπα</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Γεμιστά με κιμά</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Μπάμιες με μπούτια</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Κεφτεδάκια κοκκινιστά</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Πένες με κιμά</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Πένες αλά κρεμ</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1045,6 +1124,32 @@
       </c>
       <c r="C16" s="4" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Κεφτεδάκια τηγανητά</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Φιλετάκια κοτόπουλο αλά κρεμ</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -7,12 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Μαγειρευτά" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Της ώρας" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Συνοδευτικά" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Σαλάτες" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Γλυκά" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Αναψυκτικά - Ποτά" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Μενού Ημέρας" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Συνοδευτικά" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Σαλάτες" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Γλυκά" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Αναψυκτικά - Ποτά" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +88,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,366 +454,361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Α/Α</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Ονομασία πιάτου</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Τιμή (€)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Κοτόσουπα</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Μοσχαρόσουπα</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Γιουβαρλάκια</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>7.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Φασολάδα Πρεσπών</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>6.7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Γίγαντες Καστοριάς</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>6.7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Ρεβύθια</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>6.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Φακές</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>6.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Γεμιστά</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>6.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Μπριάμ</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>6.8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Ιμάμ</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>6.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Αρακάς</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>6.8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Μπάμιες φούρνου</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Λαχανοντολμάδες αυγολέμονο</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Σπανακόρυζο</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>6.3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Λαχανόρυζο</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Παστίτσιο</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="5" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Μουσακάς</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="5" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Παπουτσάκια</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="5" t="n">
         <v>7.8</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Σουτζουκάκια κοκκινιστά</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Μοσχαράκι γιουβέτσι</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="5" t="n">
         <v>9.5</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Μοσχαράκι κοκκινιστό</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="5" t="n">
         <v>10.5</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Μοσχαράκι λεμονάτο</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="5" t="n">
         <v>9.5</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Ρολό κοτόπουλο</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="5" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Σουφλέ ζυμαρικών</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="5" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Κριθαρότο θαλασσινών</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="5" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Σουπιές με σπανάκι</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="5" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -893,6 +888,227 @@
       </c>
       <c r="C33" s="5" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Μπιφτέκι κοτόπουλο</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Σνίτσελ κοτόπουλο</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Φιλέτο κοτόπουλο σχάρας</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Τηγανιά κοτόπουλο</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Μπριζόλα χοιρινή σχάρας</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Σουβλάκια χοιρινά μερίδα</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Κοντοσούβλι χοιρινό μερίδα</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Λουκάνικο χωριάτικο μερίδα</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Καλαμαράκια τηγανητά</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Μπακαλιάρος τηγανητός</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Γλώσσες τηγανητές</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Σολομός φούρνου</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Τσιπούρα φούρνου</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Γαρίδες τηγανητές</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Κοκορέτσι μερίδα</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Κεφτεδάκια τηγανητά</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Φιλετάκια κοτόπουλο αλά κρεμ</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -901,263 +1117,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Α/Α</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ονομασία πιάτου</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Τιμή (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Μπιφτέκι κοτόπουλο</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Σνίτσελ κοτόπουλο</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Φιλέτο κοτόπουλο σχάρας</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Τηγανιά κοτόπουλο</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Μπριζόλα χοιρινή σχάρας</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Σουβλάκια χοιρινά μερίδα</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Κοντοσούβλι χοιρινό μερίδα</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Λουκάνικο χωριάτικο μερίδα</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Καλαμαράκια τηγανητά</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Μπακαλιάρος τηγανητός</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Γλώσσες τηγανητές</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Σολομός φούρνου</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Τσιπούρα φούρνου</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Γαρίδες τηγανητές</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Κοκορέτσι μερίδα</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Κεφτεδάκια τηγανητά</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Φιλετάκια κοτόπουλο αλά κρεμ</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1269,7 +1228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1472,7 +1431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1632,7 +1591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1187,6 +1187,19 @@
       </c>
       <c r="C56" s="6" t="n">
         <v>7.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Μοσχάρι με φασολάκια</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Μενού Ημέρας" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Συνοδευτικά" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Σαλάτες" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Γλυκά" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Αναψυκτικά - Ποτά" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Μενού Ημέρας" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Συνοδευτικά" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Σαλάτες" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Γλυκά" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Αναψυκτικά - Ποτά" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1411,7 +1411,9 @@
           <t>Λάχανο &amp; καρότο</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="4" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1575,7 +1577,9 @@
           <t>Cheesecake</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="4" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1651,7 +1655,9 @@
           <t>Κανταΐφι</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1662,7 +1668,9 @@
           <t>Pancakes με μέλι</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1865,7 +1873,9 @@
           <t>Heineken 330ml</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
+      <c r="C12" s="2" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,11 @@
           <t>Τιμή (€)</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Συχνό;</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -486,6 +491,11 @@
       <c r="C2" s="6" t="n">
         <v>7.5</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -499,6 +509,11 @@
       <c r="C3" s="6" t="n">
         <v>8.5</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -512,6 +527,11 @@
       <c r="C4" s="6" t="n">
         <v>7.8</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -538,6 +558,11 @@
       <c r="C6" s="6" t="n">
         <v>6.7</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -577,6 +602,11 @@
       <c r="C9" s="6" t="n">
         <v>6.5</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -681,6 +711,11 @@
       <c r="C17" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Κ</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -694,6 +729,11 @@
       <c r="C18" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -707,6 +747,11 @@
       <c r="C19" s="6" t="n">
         <v>7.8</v>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -720,6 +765,11 @@
       <c r="C20" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -733,6 +783,11 @@
       <c r="C21" s="6" t="n">
         <v>9.5</v>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -746,6 +801,11 @@
       <c r="C22" s="6" t="n">
         <v>10.5</v>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -759,6 +819,11 @@
       <c r="C23" s="6" t="n">
         <v>9.5</v>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -772,6 +837,11 @@
       <c r="C24" s="6" t="n">
         <v>8.5</v>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -798,6 +868,11 @@
       <c r="C26" s="6" t="n">
         <v>9</v>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -928,6 +1003,11 @@
       <c r="C36" s="6" t="n">
         <v>7</v>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -954,6 +1034,11 @@
       <c r="C38" s="6" t="n">
         <v>7.5</v>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -967,6 +1052,11 @@
       <c r="C39" s="6" t="n">
         <v>7.5</v>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Κ</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -980,6 +1070,11 @@
       <c r="C40" s="6" t="n">
         <v>11.8</v>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Κ</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -993,6 +1088,11 @@
       <c r="C41" s="6" t="n">
         <v>9.5</v>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1071,6 +1171,11 @@
       <c r="C47" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1084,6 +1189,11 @@
       <c r="C48" s="6" t="n">
         <v>11.5</v>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1097,6 +1207,11 @@
       <c r="C49" s="6" t="n">
         <v>11</v>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1110,6 +1225,11 @@
       <c r="C50" s="6" t="n">
         <v>13.5</v>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Κ</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1175,6 +1295,11 @@
       <c r="C55" s="6" t="n">
         <v>9.5</v>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1187,6 +1312,11 @@
       </c>
       <c r="C56" s="6" t="n">
         <v>7.5</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
       </c>
     </row>
     <row r="57">

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,7 +574,12 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>6.5</v>
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Σ</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1207,11 +1212,6 @@
       <c r="C49" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Σ</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1330,6 +1330,19 @@
       </c>
       <c r="C57" s="6" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Μπούτι με γαρνιτούρα</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Μενού Ημέρας" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Αναψυκτικά - Ποτά" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -32,8 +31,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00F1E7D5"/>
+      <color rgb="FFF1E7D5"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -45,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B487A"/>
+        <fgColor rgb="FF2B487A"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,17 +61,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D2C4"/>
+        <color rgb="FFD9D2C4"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D2C4"/>
+        <color rgb="FFD9D2C4"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D2C4"/>
+        <color rgb="FFD9D2C4"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D2C4"/>
+        <color rgb="FFD9D2C4"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -91,7 +94,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -454,8 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="24.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -478,6 +486,11 @@
           <t>Συχνό;</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Με συνοδευτικό;</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -525,7 +538,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -543,7 +556,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -556,7 +569,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -592,7 +605,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -605,7 +618,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -623,7 +636,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -636,7 +649,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -649,7 +662,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -662,7 +675,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +701,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +763,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -775,6 +788,11 @@
           <t>Σ</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -786,7 +804,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -804,11 +822,16 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Σ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ν</t>
         </is>
       </c>
     </row>
@@ -822,11 +845,16 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Σ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ν</t>
         </is>
       </c>
     </row>
@@ -902,7 +930,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -915,7 +943,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -928,7 +956,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="31">
@@ -943,6 +971,11 @@
       <c r="C31" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -967,7 +1000,7 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -980,7 +1013,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -1006,7 +1039,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1024,7 +1057,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="38">
@@ -1044,6 +1077,11 @@
           <t>Σ</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1062,6 +1100,11 @@
           <t>Κ</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1080,6 +1123,11 @@
           <t>Κ</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1098,6 +1146,11 @@
           <t>Σ</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1111,6 +1164,11 @@
       <c r="C42" s="6" t="n">
         <v>8</v>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1124,6 +1182,11 @@
       <c r="C43" s="6" t="n">
         <v>9</v>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1137,6 +1200,11 @@
       <c r="C44" s="6" t="n">
         <v>7.5</v>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1150,6 +1218,11 @@
       <c r="C45" s="6" t="n">
         <v>9.5</v>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1163,6 +1236,11 @@
       <c r="C46" s="6" t="n">
         <v>9.5</v>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1181,6 +1259,11 @@
           <t>Σ</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1199,6 +1282,11 @@
           <t>Σ</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1212,6 +1300,11 @@
       <c r="C49" s="6" t="n">
         <v>11</v>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1230,6 +1323,11 @@
           <t>Κ</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1243,6 +1341,11 @@
       <c r="C51" s="6" t="n">
         <v>13.5</v>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1256,6 +1359,11 @@
       <c r="C52" s="6" t="n">
         <v>10</v>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1269,6 +1377,11 @@
       <c r="C53" s="6" t="n">
         <v>15</v>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1282,6 +1395,11 @@
       <c r="C54" s="6" t="n">
         <v>10.5</v>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ν</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1316,6 +1434,11 @@
       <c r="D56" t="inlineStr">
         <is>
           <t>Σ</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ν</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1480,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -1469,7 +1592,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -1674,7 +1797,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -1853,7 +1976,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>11.8</v>
+        <v>8.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="36">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="30">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1466,6 +1466,227 @@
       </c>
       <c r="C58" t="n">
         <v>7.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Μελιτζάνες φούρνου με ντομάτα &amp; φέτα</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Κολοκυθάκια γεμιστά</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Κολοκυθάκια αυγολέμονο</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Χοιρινό με πράσο στο φούρνο</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Χοιρινή τηγανιά</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Μοσχαράκι με μελιτζάνες</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Μπούτι κοτόπουλο με φασολάκια</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Φασολάκια πλατιά</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Κριθαρότο με λαχανικά</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Χταπόδι στιφάδο</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Γαρίδες κοκκινιστές</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Γαρίδες κριθαρότο</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Γαριδομακαρονάδα</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Μπακαλιάρος στιφάδο</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Παστίτσιο νηστίσιμο</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Μουσακάς νηστίσιμος</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Κολοκυθάκια νηστίσιμα</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>

--- a/DAILY_MENU.xlsx
+++ b/DAILY_MENU.xlsx
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Φιλέτο κοτόπουλο σχάρας</t>
+          <t>Φιλέτο κοτόπουλο</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
